--- a/合同全生命周期管理系统-项目管理套件/09_上线移交与运营/旧合同系统迁移管理-20260920-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/09_上线移交与运营/旧合同系统迁移管理-20260920-V1.xlsx
@@ -804,7 +804,7 @@
           <t>字段</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="25" t="inlineStr">
         <is>
           <t>值</t>
         </is>
@@ -816,7 +816,7 @@
           <t>Project_ID</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>ECM-2026</t>
         </is>
@@ -828,7 +828,7 @@
           <t>项目名称</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>能源行业合同全生命周期管理系统</t>
         </is>
@@ -840,7 +840,7 @@
           <t>模块编码</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>09</t>
         </is>
@@ -852,7 +852,7 @@
           <t>数据日期</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="26" t="n">
         <v>46285</v>
       </c>
     </row>
@@ -862,7 +862,7 @@
           <t>文件性质</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>G15 评审草案，未替代正式 MIG 台账</t>
         </is>
@@ -874,9 +874,9 @@
           <t>来源线索数</t>
         </is>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="21">
         <f>COUNTIF(来源系统盘点!$A$5:$A$100,"&lt;&gt;")</f>
-        <v>6</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -885,9 +885,9 @@
           <t>已盘点来源系统数</t>
         </is>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="21">
         <f>COUNTIFS(来源系统盘点!$D$5:$D$100,"&lt;&gt;待盘点",来源系统盘点!$D$5:$D$100,"&lt;&gt;")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -896,9 +896,9 @@
           <t>迁移对象数</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="21">
         <f>COUNTIF(对象范围盘点!$A$5:$A$100,"&lt;&gt;")</f>
-        <v>9</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -907,9 +907,9 @@
           <t>迁移工作包数</t>
         </is>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="21">
         <f>COUNTIF(迁移任务分解!$A$5:$A$100,"&lt;&gt;")</f>
-        <v>13</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -918,9 +918,9 @@
           <t>迁移门禁数</t>
         </is>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="21">
         <f>COUNTIF(门禁与演练!$A$5:$A$100,"&lt;&gt;")</f>
-        <v>7</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -929,7 +929,7 @@
           <t>G15 目标日期</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="26" t="n">
         <v>46308</v>
       </c>
     </row>
@@ -939,7 +939,7 @@
           <t>中央数据库</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>../90_项目数据中心/ai_pmo.db</t>
         </is>
@@ -953,7 +953,7 @@
       </c>
       <c r="B14" s="21">
         <f>COUNTIF(盘点进度!$E$7:$E$200,"已完成")</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -964,7 +964,7 @@
       </c>
       <c r="B15" s="21">
         <f>COUNTIF(盘点进度!$A$7:$A$200,"SRC-*")</f>
-        <v>48</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B3">
         <f>COUNTIF($E$7:$E$200,"已完成")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="D3">
         <f>COUNTIF($A$7:$A$200,"SRC-*")</f>
-        <v>48</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B4" s="24">
         <f>IF(D3=0,"",B3/D3)</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>档案代表、测试人员</t>
+          <t>档案代表、高级测试人员、中级测试人员</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>技术经理、测试人员</t>
+          <t>技术经理、高级测试人员、中级测试人员</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">

--- a/合同全生命周期管理系统-项目管理套件/09_上线移交与运营/旧合同系统迁移管理-20260920-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/09_上线移交与运营/旧合同系统迁移管理-20260920-V1.xlsx
@@ -3,6 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="迁移策略" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对象范围盘点" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源系统盘点" sheetId="3" state="visible" r:id="rId3"/>
@@ -11,7 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="责任矩阵" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="门禁与演练" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="迁移任务分解" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_数据接口" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="盘点进度" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
